--- a/employment_forms/011_crews_shoes_order_form--employment_forms.xlsx
+++ b/employment_forms/011_crews_shoes_order_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'replacement'}</t>
+          <t>replacement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Replacement'}</t>
+          <t>Replacement</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'repair'}</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Repair'}</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'new',_'selected':_true}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'New', 'selected': True}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'selected':_false}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'selected': False}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'selected':_false}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'selected': False}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'done',_'selected':_false}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Done', 'selected': False}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'dress'}</t>
+          <t>dress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Dress'}</t>
+          <t>Dress</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'athletic'}</t>
+          <t>athletic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Athletic'}</t>
+          <t>Athletic</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'boots'}</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Boots'}</t>
+          <t>Boots</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sandals'}</t>
+          <t>sandals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sandals'}</t>
+          <t>Sandals</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'sneakers'}</t>
+          <t>sneakers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Sneakers'}</t>
+          <t>Sneakers</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'yellow'}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Yellow'}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'converse'}</t>
+          <t>converse</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Converse'}</t>
+          <t>Converse</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'vans'}</t>
+          <t>vans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Vans'}</t>
+          <t>Vans</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'adidas'}</t>
+          <t>adidas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Adidas'}</t>
+          <t>Adidas</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'nike'}</t>
+          <t>nike</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Nike'}</t>
+          <t>Nike</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
